--- a/GameConfig/Datas/_import_v1_preview/剧情节点配置表.xlsx
+++ b/GameConfig/Datas/_import_v1_preview/剧情节点配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剧情节点配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="剧情节点配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O266"/>
+  <dimension ref="A1:P266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -430,6 +430,7 @@
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,6 +509,11 @@
           <t>priority</t>
         </is>
       </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>backgroundId</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -585,6 +591,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -662,6 +673,11 @@
           <t>c</t>
         </is>
       </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -737,6 +753,11 @@
       <c r="O4" t="inlineStr">
         <is>
           <t>节点优先级</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>本节点起切换到的场景 ID；为空表示沿用所属 Session 的 backgroundId</t>
         </is>
       </c>
     </row>
@@ -788,6 +809,7 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -837,6 +859,7 @@
       <c r="O6" t="n">
         <v>1</v>
       </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -886,6 +909,7 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -935,6 +959,7 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -984,6 +1009,7 @@
       <c r="O9" t="n">
         <v>1</v>
       </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1033,6 +1059,7 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1094,6 +1121,7 @@
       <c r="O11" t="n">
         <v>1</v>
       </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1143,6 +1171,7 @@
       <c r="O12" t="n">
         <v>1</v>
       </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1192,6 +1221,7 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -1241,6 +1271,7 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1290,6 +1321,7 @@
       <c r="O15" t="n">
         <v>1</v>
       </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1339,6 +1371,7 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1388,6 +1421,7 @@
       <c r="O17" t="n">
         <v>1</v>
       </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1437,6 +1471,7 @@
       <c r="O18" t="n">
         <v>1</v>
       </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1486,6 +1521,7 @@
       <c r="O19" t="n">
         <v>1</v>
       </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1535,6 +1571,7 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
@@ -1584,6 +1621,7 @@
       <c r="O21" t="n">
         <v>1</v>
       </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
@@ -1633,6 +1671,7 @@
       <c r="O22" t="n">
         <v>1</v>
       </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
@@ -1682,6 +1721,7 @@
       <c r="O23" t="n">
         <v>1</v>
       </c>
+      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
@@ -1731,6 +1771,7 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
@@ -1780,6 +1821,7 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
@@ -1829,6 +1871,7 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
@@ -1878,6 +1921,7 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
@@ -1927,6 +1971,7 @@
       <c r="O28" t="n">
         <v>1</v>
       </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
@@ -1976,6 +2021,7 @@
       <c r="O29" t="n">
         <v>1</v>
       </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
@@ -2025,6 +2071,7 @@
       <c r="O30" t="n">
         <v>1</v>
       </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
@@ -2074,6 +2121,7 @@
       <c r="O31" t="n">
         <v>1</v>
       </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
@@ -2123,6 +2171,7 @@
       <c r="O32" t="n">
         <v>1</v>
       </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
@@ -2172,6 +2221,7 @@
       <c r="O33" t="n">
         <v>1</v>
       </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
@@ -2221,6 +2271,7 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
@@ -2270,6 +2321,7 @@
       <c r="O35" t="n">
         <v>1</v>
       </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
@@ -2319,6 +2371,7 @@
       <c r="O36" t="n">
         <v>1</v>
       </c>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
@@ -2368,6 +2421,7 @@
       <c r="O37" t="n">
         <v>1</v>
       </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
@@ -2425,6 +2479,7 @@
       <c r="O38" t="n">
         <v>1</v>
       </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
@@ -2482,6 +2537,7 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
@@ -2531,6 +2587,7 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
@@ -2580,6 +2637,7 @@
       <c r="O41" t="n">
         <v>10</v>
       </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
@@ -2629,6 +2687,7 @@
       <c r="O42" t="n">
         <v>1</v>
       </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
@@ -2690,6 +2749,7 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
@@ -2739,6 +2799,7 @@
       <c r="O44" t="n">
         <v>1</v>
       </c>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
@@ -2788,6 +2849,7 @@
       <c r="O45" t="n">
         <v>1</v>
       </c>
+      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
@@ -2837,6 +2899,7 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
@@ -2886,6 +2949,7 @@
       <c r="O47" t="n">
         <v>1</v>
       </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
@@ -2935,6 +2999,7 @@
       <c r="O48" t="n">
         <v>1</v>
       </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
@@ -2984,6 +3049,7 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
@@ -3033,6 +3099,7 @@
       <c r="O50" t="n">
         <v>1</v>
       </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
@@ -3082,6 +3149,7 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
@@ -3127,6 +3195,7 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
@@ -3176,6 +3245,7 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
@@ -3225,6 +3295,7 @@
       <c r="O54" t="n">
         <v>1</v>
       </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
@@ -3274,6 +3345,7 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
@@ -3323,6 +3395,7 @@
       <c r="O56" t="n">
         <v>1</v>
       </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
@@ -3372,6 +3445,7 @@
       <c r="O57" t="n">
         <v>1</v>
       </c>
+      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
@@ -3421,6 +3495,7 @@
       <c r="O58" t="n">
         <v>1</v>
       </c>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
@@ -3470,6 +3545,7 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -3519,6 +3595,7 @@
       <c r="O60" t="n">
         <v>1</v>
       </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
@@ -3568,6 +3645,7 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
@@ -3617,6 +3695,7 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
@@ -3666,6 +3745,7 @@
       <c r="O63" t="n">
         <v>1</v>
       </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
@@ -3715,6 +3795,7 @@
       <c r="O64" t="n">
         <v>1</v>
       </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
@@ -3772,6 +3853,7 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
@@ -3821,6 +3903,7 @@
       <c r="O66" t="n">
         <v>1</v>
       </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
@@ -3874,6 +3957,7 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
@@ -3923,6 +4007,7 @@
       <c r="O68" t="n">
         <v>1</v>
       </c>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
@@ -3972,6 +4057,7 @@
       <c r="O69" t="n">
         <v>1</v>
       </c>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
@@ -4021,6 +4107,7 @@
       <c r="O70" t="n">
         <v>1</v>
       </c>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
@@ -4070,6 +4157,7 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
+      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
@@ -4119,6 +4207,7 @@
       <c r="O72" t="n">
         <v>1</v>
       </c>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
@@ -4168,6 +4257,7 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
@@ -4217,6 +4307,7 @@
       <c r="O74" t="n">
         <v>1</v>
       </c>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
@@ -4266,6 +4357,7 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
@@ -4315,6 +4407,7 @@
       <c r="O76" t="n">
         <v>1</v>
       </c>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
@@ -4360,6 +4453,7 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
@@ -4417,6 +4511,7 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
@@ -4466,6 +4561,7 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
+      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
@@ -4515,6 +4611,7 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
+      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
@@ -4568,6 +4665,7 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
@@ -4617,6 +4715,7 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
@@ -4666,6 +4765,7 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
@@ -4715,6 +4815,7 @@
       <c r="O84" t="n">
         <v>1</v>
       </c>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
@@ -4764,6 +4865,7 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
+      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
@@ -4813,6 +4915,7 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
@@ -4858,6 +4961,7 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
@@ -4907,6 +5011,7 @@
       <c r="O88" t="n">
         <v>1</v>
       </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
@@ -4956,6 +5061,7 @@
       <c r="O89" t="n">
         <v>1</v>
       </c>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
@@ -5005,6 +5111,7 @@
       <c r="O90" t="n">
         <v>1</v>
       </c>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
@@ -5054,6 +5161,7 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
@@ -5103,6 +5211,7 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
+      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
@@ -5152,6 +5261,7 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
@@ -5201,6 +5311,7 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
@@ -5250,6 +5361,7 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
@@ -5311,6 +5423,7 @@
       <c r="O96" t="n">
         <v>1</v>
       </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
@@ -5360,6 +5473,7 @@
       <c r="O97" t="n">
         <v>1</v>
       </c>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
@@ -5409,6 +5523,7 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
@@ -5458,6 +5573,7 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
@@ -5507,6 +5623,7 @@
       <c r="O100" t="n">
         <v>1</v>
       </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
@@ -5556,6 +5673,7 @@
       <c r="O101" t="n">
         <v>1</v>
       </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
@@ -5605,6 +5723,7 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
@@ -5654,6 +5773,7 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
+      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
@@ -5703,6 +5823,7 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
+      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
@@ -5752,6 +5873,7 @@
       <c r="O105" t="n">
         <v>1</v>
       </c>
+      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
@@ -5801,6 +5923,7 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
+      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
@@ -5850,6 +5973,7 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
@@ -5899,6 +6023,7 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
+      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
@@ -5948,6 +6073,7 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
+      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
@@ -5997,6 +6123,7 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
+      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
@@ -6046,6 +6173,7 @@
       <c r="O111" t="n">
         <v>1</v>
       </c>
+      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
@@ -6095,6 +6223,7 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
+      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
@@ -6144,6 +6273,7 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
@@ -6193,6 +6323,7 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
@@ -6242,6 +6373,7 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
@@ -6291,6 +6423,7 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
@@ -6344,6 +6477,7 @@
       <c r="O117" t="n">
         <v>1</v>
       </c>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
@@ -6397,6 +6531,7 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
@@ -6446,6 +6581,7 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
@@ -6495,6 +6631,7 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
@@ -6544,6 +6681,7 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
@@ -6593,6 +6731,7 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
@@ -6642,6 +6781,7 @@
       <c r="O123" t="n">
         <v>1</v>
       </c>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
@@ -6691,6 +6831,7 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
@@ -6740,6 +6881,7 @@
       <c r="O125" t="n">
         <v>1</v>
       </c>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
@@ -6789,6 +6931,7 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
@@ -6838,6 +6981,7 @@
       <c r="O127" t="n">
         <v>1</v>
       </c>
+      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
@@ -6887,6 +7031,7 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
@@ -6936,6 +7081,7 @@
       <c r="O129" t="n">
         <v>1</v>
       </c>
+      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
@@ -6985,6 +7131,7 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
@@ -7034,6 +7181,7 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
+      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
@@ -7083,6 +7231,7 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
+      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
@@ -7136,6 +7285,7 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
+      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
@@ -7185,6 +7335,7 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
@@ -7234,6 +7385,7 @@
       <c r="O135" t="n">
         <v>1</v>
       </c>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
@@ -7283,6 +7435,7 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
@@ -7332,6 +7485,7 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
@@ -7381,6 +7535,7 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
@@ -7430,6 +7585,7 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
@@ -7479,6 +7635,7 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
@@ -7528,6 +7685,7 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
+      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
@@ -7577,6 +7735,7 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
@@ -7622,6 +7781,7 @@
       <c r="O143" t="n">
         <v>1</v>
       </c>
+      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
@@ -7671,6 +7831,7 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
@@ -7720,6 +7881,7 @@
       <c r="O145" t="n">
         <v>1</v>
       </c>
+      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
@@ -7769,6 +7931,7 @@
       <c r="O146" t="n">
         <v>1</v>
       </c>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
@@ -7818,6 +7981,7 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
@@ -7867,6 +8031,7 @@
       <c r="O148" t="n">
         <v>1</v>
       </c>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
@@ -7916,6 +8081,7 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
@@ -7977,6 +8143,7 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
@@ -8026,6 +8193,7 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -8075,6 +8243,7 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -8124,6 +8293,7 @@
       <c r="O153" t="n">
         <v>1</v>
       </c>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -8173,6 +8343,7 @@
       <c r="O154" t="n">
         <v>1</v>
       </c>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -8222,6 +8393,7 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
+      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
@@ -8271,6 +8443,7 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
+      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -8320,6 +8493,7 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
+      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -8369,6 +8543,7 @@
       <c r="O158" t="n">
         <v>1</v>
       </c>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -8418,6 +8593,7 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -8467,6 +8643,7 @@
       <c r="O160" t="n">
         <v>1</v>
       </c>
+      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
@@ -8516,6 +8693,7 @@
       <c r="O161" t="n">
         <v>1</v>
       </c>
+      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -8565,6 +8743,7 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
+      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -8614,6 +8793,7 @@
       <c r="O163" t="n">
         <v>1</v>
       </c>
+      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -8663,6 +8843,7 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
+      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -8712,6 +8893,7 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
+      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
@@ -8761,6 +8943,7 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
+      <c r="P166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -8810,6 +8993,7 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
+      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -8859,6 +9043,7 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
+      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -8908,6 +9093,7 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -8957,6 +9143,7 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
+      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
@@ -9006,6 +9193,7 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
+      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -9055,6 +9243,7 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
+      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
@@ -9104,6 +9293,7 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
+      <c r="P173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
@@ -9153,6 +9343,7 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
+      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
@@ -9202,6 +9393,7 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
+      <c r="P175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
@@ -9251,6 +9443,7 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
+      <c r="P176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
@@ -9300,6 +9493,7 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
+      <c r="P177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
@@ -9349,6 +9543,7 @@
       <c r="O178" t="n">
         <v>1</v>
       </c>
+      <c r="P178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
@@ -9398,6 +9593,7 @@
       <c r="O179" t="n">
         <v>1</v>
       </c>
+      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
@@ -9447,6 +9643,7 @@
       <c r="O180" t="n">
         <v>1</v>
       </c>
+      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
@@ -9496,6 +9693,7 @@
       <c r="O181" t="n">
         <v>1</v>
       </c>
+      <c r="P181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
@@ -9545,6 +9743,7 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
+      <c r="P182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
@@ -9594,6 +9793,7 @@
       <c r="O183" t="n">
         <v>1</v>
       </c>
+      <c r="P183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
@@ -9643,6 +9843,7 @@
       <c r="O184" t="n">
         <v>1</v>
       </c>
+      <c r="P184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
@@ -9692,6 +9893,7 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
+      <c r="P185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
@@ -9741,6 +9943,7 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
+      <c r="P186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
@@ -9790,6 +9993,7 @@
       <c r="O187" t="n">
         <v>1</v>
       </c>
+      <c r="P187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
@@ -9839,6 +10043,7 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
+      <c r="P188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
@@ -9892,6 +10097,7 @@
       <c r="O189" t="n">
         <v>1</v>
       </c>
+      <c r="P189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
@@ -9941,6 +10147,7 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
+      <c r="P190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
@@ -9990,6 +10197,7 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
+      <c r="P191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
@@ -10039,6 +10247,7 @@
       <c r="O192" t="n">
         <v>1</v>
       </c>
+      <c r="P192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
@@ -10088,6 +10297,7 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
+      <c r="P193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
@@ -10137,6 +10347,7 @@
       <c r="O194" t="n">
         <v>1</v>
       </c>
+      <c r="P194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
@@ -10186,6 +10397,7 @@
       <c r="O195" t="n">
         <v>1</v>
       </c>
+      <c r="P195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
@@ -10235,6 +10447,7 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
+      <c r="P196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
@@ -10284,6 +10497,7 @@
       <c r="O197" t="n">
         <v>1</v>
       </c>
+      <c r="P197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
@@ -10333,6 +10547,7 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
+      <c r="P198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
@@ -10382,6 +10597,7 @@
       <c r="O199" t="n">
         <v>1</v>
       </c>
+      <c r="P199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
@@ -10431,6 +10647,7 @@
       <c r="O200" t="n">
         <v>1</v>
       </c>
+      <c r="P200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
@@ -10480,6 +10697,7 @@
       <c r="O201" t="n">
         <v>1</v>
       </c>
+      <c r="P201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
@@ -10529,6 +10747,7 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
+      <c r="P202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
@@ -10574,6 +10793,7 @@
       <c r="O203" t="n">
         <v>1</v>
       </c>
+      <c r="P203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
@@ -10623,6 +10843,7 @@
       <c r="O204" t="n">
         <v>1</v>
       </c>
+      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
@@ -10672,6 +10893,7 @@
       <c r="O205" t="n">
         <v>1</v>
       </c>
+      <c r="P205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
@@ -10721,6 +10943,7 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
+      <c r="P206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
@@ -10770,6 +10993,7 @@
       <c r="O207" t="n">
         <v>1</v>
       </c>
+      <c r="P207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
@@ -10819,6 +11043,7 @@
       <c r="O208" t="n">
         <v>1</v>
       </c>
+      <c r="P208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
@@ -10868,6 +11093,7 @@
       <c r="O209" t="n">
         <v>1</v>
       </c>
+      <c r="P209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
@@ -10921,6 +11147,7 @@
       <c r="O210" t="n">
         <v>1</v>
       </c>
+      <c r="P210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
@@ -10970,6 +11197,7 @@
       <c r="O211" t="n">
         <v>1</v>
       </c>
+      <c r="P211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
@@ -11019,6 +11247,7 @@
       <c r="O212" t="n">
         <v>1</v>
       </c>
+      <c r="P212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
@@ -11068,6 +11297,7 @@
       <c r="O213" t="n">
         <v>1</v>
       </c>
+      <c r="P213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
@@ -11117,6 +11347,7 @@
       <c r="O214" t="n">
         <v>1</v>
       </c>
+      <c r="P214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
@@ -11166,6 +11397,7 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
+      <c r="P215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>
@@ -11215,6 +11447,7 @@
       <c r="O216" t="n">
         <v>1</v>
       </c>
+      <c r="P216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
@@ -11264,6 +11497,7 @@
       <c r="O217" t="n">
         <v>1</v>
       </c>
+      <c r="P217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr"/>
@@ -11313,6 +11547,7 @@
       <c r="O218" t="n">
         <v>1</v>
       </c>
+      <c r="P218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
@@ -11366,6 +11601,7 @@
       <c r="O219" t="n">
         <v>1</v>
       </c>
+      <c r="P219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
@@ -11415,6 +11651,7 @@
       <c r="O220" t="n">
         <v>1</v>
       </c>
+      <c r="P220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>
@@ -11464,6 +11701,7 @@
       <c r="O221" t="n">
         <v>1</v>
       </c>
+      <c r="P221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
@@ -11513,6 +11751,7 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
+      <c r="P222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
@@ -11562,6 +11801,7 @@
       <c r="O223" t="n">
         <v>1</v>
       </c>
+      <c r="P223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
@@ -11611,6 +11851,7 @@
       <c r="O224" t="n">
         <v>1</v>
       </c>
+      <c r="P224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
@@ -11660,6 +11901,7 @@
       <c r="O225" t="n">
         <v>1</v>
       </c>
+      <c r="P225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr"/>
@@ -11705,6 +11947,7 @@
       <c r="O226" t="n">
         <v>1</v>
       </c>
+      <c r="P226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr"/>
@@ -11754,6 +11997,7 @@
       <c r="O227" t="n">
         <v>1</v>
       </c>
+      <c r="P227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
@@ -11803,6 +12047,7 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
+      <c r="P228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
@@ -11852,6 +12097,7 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
+      <c r="P229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr"/>
@@ -11901,6 +12147,7 @@
       <c r="O230" t="n">
         <v>1</v>
       </c>
+      <c r="P230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
@@ -11950,6 +12197,7 @@
       <c r="O231" t="n">
         <v>1</v>
       </c>
+      <c r="P231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
@@ -12003,6 +12251,7 @@
       <c r="O232" t="n">
         <v>1</v>
       </c>
+      <c r="P232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr"/>
@@ -12052,6 +12301,7 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
+      <c r="P233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr"/>
@@ -12101,6 +12351,7 @@
       <c r="O234" t="n">
         <v>1</v>
       </c>
+      <c r="P234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr"/>
@@ -12150,6 +12401,7 @@
       <c r="O235" t="n">
         <v>1</v>
       </c>
+      <c r="P235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr"/>
@@ -12199,6 +12451,7 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
+      <c r="P236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr"/>
@@ -12248,6 +12501,7 @@
       <c r="O237" t="n">
         <v>1</v>
       </c>
+      <c r="P237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr"/>
@@ -12297,6 +12551,7 @@
       <c r="O238" t="n">
         <v>1</v>
       </c>
+      <c r="P238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr"/>
@@ -12346,6 +12601,7 @@
       <c r="O239" t="n">
         <v>1</v>
       </c>
+      <c r="P239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr"/>
@@ -12395,6 +12651,7 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
+      <c r="P240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr"/>
@@ -12444,6 +12701,7 @@
       <c r="O241" t="n">
         <v>1</v>
       </c>
+      <c r="P241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr"/>
@@ -12493,6 +12751,7 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
+      <c r="P242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr"/>
@@ -12542,6 +12801,7 @@
       <c r="O243" t="n">
         <v>1</v>
       </c>
+      <c r="P243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr"/>
@@ -12591,6 +12851,7 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
+      <c r="P244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
@@ -12640,6 +12901,7 @@
       <c r="O245" t="n">
         <v>1</v>
       </c>
+      <c r="P245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr"/>
@@ -12689,6 +12951,7 @@
       <c r="O246" t="n">
         <v>1</v>
       </c>
+      <c r="P246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr"/>
@@ -12738,6 +13001,7 @@
       <c r="O247" t="n">
         <v>1</v>
       </c>
+      <c r="P247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr"/>
@@ -12787,6 +13051,7 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
+      <c r="P248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr"/>
@@ -12836,6 +13101,7 @@
       <c r="O249" t="n">
         <v>1</v>
       </c>
+      <c r="P249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr"/>
@@ -12885,6 +13151,7 @@
       <c r="O250" t="n">
         <v>1</v>
       </c>
+      <c r="P250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr"/>
@@ -12934,6 +13201,7 @@
       <c r="O251" t="n">
         <v>1</v>
       </c>
+      <c r="P251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr"/>
@@ -12983,6 +13251,7 @@
       <c r="O252" t="n">
         <v>1</v>
       </c>
+      <c r="P252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr"/>
@@ -13032,6 +13301,7 @@
       <c r="O253" t="n">
         <v>1</v>
       </c>
+      <c r="P253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr"/>
@@ -13081,6 +13351,7 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
+      <c r="P254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr"/>
@@ -13130,6 +13401,7 @@
       <c r="O255" t="n">
         <v>1</v>
       </c>
+      <c r="P255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr"/>
@@ -13179,6 +13451,7 @@
       <c r="O256" t="n">
         <v>1</v>
       </c>
+      <c r="P256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr"/>
@@ -13228,6 +13501,7 @@
       <c r="O257" t="n">
         <v>1</v>
       </c>
+      <c r="P257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr"/>
@@ -13277,6 +13551,7 @@
       <c r="O258" t="n">
         <v>1</v>
       </c>
+      <c r="P258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr"/>
@@ -13326,6 +13601,7 @@
       <c r="O259" t="n">
         <v>1</v>
       </c>
+      <c r="P259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr"/>
@@ -13375,6 +13651,7 @@
       <c r="O260" t="n">
         <v>1</v>
       </c>
+      <c r="P260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr"/>
@@ -13424,6 +13701,7 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
+      <c r="P261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr"/>
@@ -13473,6 +13751,7 @@
       <c r="O262" t="n">
         <v>1</v>
       </c>
+      <c r="P262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr"/>
@@ -13522,6 +13801,7 @@
       <c r="O263" t="n">
         <v>1</v>
       </c>
+      <c r="P263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr"/>
@@ -13571,6 +13851,7 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
+      <c r="P264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr"/>
@@ -13620,6 +13901,7 @@
       <c r="O265" t="n">
         <v>1</v>
       </c>
+      <c r="P265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr"/>
@@ -13665,6 +13947,7 @@
       <c r="O266" t="n">
         <v>1</v>
       </c>
+      <c r="P266" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
